--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_036_Australia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_036_Australia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R73a6f745d43348a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf894467894aa4534"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R357dcec1688448e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rdf27a8cdf29e48ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8ca8bea217d8491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5d981a372806456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R860d19118e9c48fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf8989723375740f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfd9ccb6343b04960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R384e485195464456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R15a21cd6c0a040af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R22cb8deb9c9b4c3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ036CommercialTable" displayName="EEZ036CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ036CommercialTable" displayName="EEZ036CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ036FunctionalTable" displayName="EEZ036FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ036FunctionalTable" displayName="EEZ036FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ036ValidationTable" displayName="EEZ036ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ036ValidationTable" displayName="EEZ036ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -36137,7 +36091,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf23e1d3308d4324"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5718936e2d3b4bc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36147,20 +36101,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -36168,660 +36112,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>343.020688264</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.200223458009218</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.57088790986657</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>343.020688264</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.621420645689</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$530,A2,'Species'!$U$2:$U$530))</x:f>
-        <x:v>54410.4288832977</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.200223458009218</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.57088790986657</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>54393.095109476024</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>17.333773821679642</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0003186759971425</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00031867599714250976</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2413.9171680922</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.334266339439726</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2159.068093237039</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2413.9171680922</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2637.949588284442</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$530,A3,'Species'!$U$2:$U$530))</x:f>
-        <x:v>6367791.799721565</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.334266339439726</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2159.068093237039</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5211811.53734498</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1155980.262376585</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.221800088912169</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.22180008891216904</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>36196.5074032869</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9775924870266106</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>94.97132278837559</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>36196.5074032869</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>153.16209873819454</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$530,A4,'Species'!$U$2:$U$530))</x:f>
-        <x:v>5543933.040880018</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9775924870266106</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>94.97132278837559</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3437630.188409387</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2106302.852470631</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.6127194424730225</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.6127194424730225</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>194.4130665186</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.7065692163964754</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>508.8259081476797</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>194.4130665186</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>547.5518392733687</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$530,A5,'Species'!$U$2:$U$530))</x:f>
-        <x:v>106451.2321510352</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.7065692163964754</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>508.8259081476797</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>98922.40512710191</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>7528.827023933292</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0761084105694738</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0761084105694738</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>37432.296731388305</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.8357252486860083</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>68.50546975081642</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>37432.296731388305</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>69.41405129282683</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$530,A6,'Species'!$U$2:$U$530))</x:f>
-        <x:v>2598327.365320902</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.8357252486860083</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>68.50546975081642</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2564317.0714357058</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>34010.29388519609</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.013262905068972</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.013262905068972014</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6303.2453657001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.012134631716994</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.283350335926734</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6303.2453657001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.688051417099839</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$530,A7,'Species'!$U$2:$U$530))</x:f>
-        <x:v>67369.41056319894</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.012134631716994</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.283350335926734</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>64818.48034880075</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2550.930214398184</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0393549833422682</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.03935498334226807</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>32455.537807257602</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4717389270780448</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>296.30496386169483</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>32455.537807257602</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>469.5219093899335</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$530,A8,'Species'!$U$2:$U$530))</x:f>
-        <x:v>15238586.081540765</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4717389270780448</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>296.30496386169483</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>9616736.957091333</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5621849.124449432</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.5845900901244792</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5845900901244792</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>78758.3402441443</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.749978639551373</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>562.3136675338607</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>78758.3402441443</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1025.100797381171</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$530,A9,'Species'!$U$2:$U$530))</x:f>
-        <x:v>80735237.38468991</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.749978639551373</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>562.3136675338607</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>44286891.15156444</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>36448346.23312547</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.8230053021420523</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8230053021420521</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6616.788501606</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.840420282542166</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>692.5008049334059</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6616.788501606</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>716.3362003042199</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$530,A10,'Species'!$U$2:$U$530))</x:f>
-        <x:v>4739845.133457094</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.840420282542166</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>692.5008049334059</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4582131.363436259</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>157713.7700208351</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0344193034881832</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03441930348818316</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>10731.3688560147</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.135224784652136</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1365.2896082425991</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>10731.3688560147</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1568.6228048912178</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$530,A11,'Species'!$U$2:$U$530))</x:f>
-        <x:v>16833469.91524404</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.135224784652136</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1365.2896082425991</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>14651426.38133514</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2182043.5339089</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.148930450668521</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.14893045066852098</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>17359.3177119627</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.11850350540575</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1313.7220986186514</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>17359.3177119627</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1546.7405771098022</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$530,A12,'Species'!$U$2:$U$530))</x:f>
-        <x:v>26850361.096033596</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.11850350540575</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1313.7220986186514</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>22805319.295147564</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>4045041.8008860312</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1773727325864156</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.17737273258641553</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb03df9a8ca1649d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3173d3cc8e24e38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36831,20 +36346,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -36852,1470 +36357,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4666.396637667101</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8461073925773483</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>701.6287761182981</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4666.396637667101</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>754.9141376113577</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$530,A2,'Species'!$U$2:$U$530))</x:f>
-        <x:v>3522728.7934769983</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8461073925773483</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>701.6287761182981</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3274078.161768909</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>248650.63170808926</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0759452338711881</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07594523387118805</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.92</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.92</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$530,A3,'Species'!$U$2:$U$530))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>265.3308982876477</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>265.3308982876477</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1993.1105344302</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.122133409073063</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1324.7484165238864</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1993.1105344302</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1417.1322104774886</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$530,A4,'Species'!$U$2:$U$530))</x:f>
-        <x:v>2824501.1373830377</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.122133409073063</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1324.7484165238864</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2640370.0244434844</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>184131.11293955334</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0697368593170433</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.06973685931704325</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>75.290650177</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.2044576385714425</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1601.2444540715198</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>75.290650177</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1616.7883624791261</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$530,A5,'Species'!$U$2:$U$530))</x:f>
-        <x:v>121729.04700966056</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.2044576385714425</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1601.2444540715198</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>120558.73603936016</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1170.310970300401</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.009707392502177</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.009707392502176835</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5975.8497873758</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.911492647855504</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>81.56289792832305</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5975.8497873758</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>436.8495616437744</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$530,A6,'Species'!$U$2:$U$530))</x:f>
-        <x:v>2610547.3600641605</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.911492647855504</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>81.56289792832305</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>487407.6262427234</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2123139.733821437</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>5.355983820335503</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>4.355983820335503</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9897.300784830999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.135629444873259</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1366.5623296048643</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9897.300784830999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1838.5263493898908</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$530,A7,'Species'!$U$2:$U$530))</x:f>
-        <x:v>18196448.280749038</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.135629444873259</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1366.5623296048643</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>13525278.417318702</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4671169.863430336</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.345365893351892</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3453658933518919</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22377.3970524731</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.195046818632903</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1566.9199810666762</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22377.3970524731</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1867.6152588221512</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$530,A8,'Species'!$U$2:$U$530))</x:f>
-        <x:v>41792368.18792059</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.195046818632903</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1566.9199810666762</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>35063590.565782644</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>6728777.622137949</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1919021273509944</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.19190212735099446</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>659.0726634714001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.659863887184146</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>456.94495543930617</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>659.0726634714001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>549.3744805992051</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$530,A9,'Species'!$U$2:$U$530))</x:f>
-        <x:v>362077.7021717351</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.659863887184146</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>456.94495543930617</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>301159.92884120374</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>60917.773330531374</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2022771540853041</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.20227715408530406</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2070.2582092126</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.023162931621592</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1054.7825385264152</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2070.2582092126</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1435.6167123787498</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$530,A10,'Species'!$U$2:$U$530))</x:f>
-        <x:v>2972097.2840849105</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.023162931621592</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1054.7825385264152</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2183672.2093184167</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>788425.0747664939</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3610546818345886</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.3610546818345885</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9780.926953599599</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.183225474597988</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1524.8442084784804</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9780.926953599599</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1671.4390538223672</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$530,A11,'Species'!$U$2:$U$530))</x:f>
-        <x:v>16348223.292830203</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.183225474597988</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1524.8442084784804</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>14914389.818747414</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1433833.4740827885</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.09613758869843</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.09613758869842984</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>20615.3643552343</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.872583339314804</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>74.57329613690975</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>20615.3643552343</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>128.46476213968987</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$530,A12,'Species'!$U$2:$U$530))</x:f>
-        <x:v>2648347.8783182153</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.872583339314804</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>74.57329613690975</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1537355.6710331808</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1110992.2072850345</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.7226643958963586</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.7226643958963586</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1623.9639433182</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.8216385220546725</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>663.1908445074496</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1623.9639433182</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>954.7120961631048</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$530,A13,'Species'!$U$2:$U$530))</x:f>
-        <x:v>1550418.0204186202</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.8216385220546725</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>663.1908445074496</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1076998.0190188452</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>473420.00139977504</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.4395736974809525</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.43957369748095254</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>902.1833698214001</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.950485610234912</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>892.2480556556012</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>902.1833698214001</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1064.4198985402068</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$530,A14,'Species'!$U$2:$U$530))</x:f>
-        <x:v>960301.9309699566</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.950485610234912</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>892.2480556556012</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>804971.3575679625</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>155330.57340199407</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1929640998299493</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.19296409982994922</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>20103.2095380974</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.7629579410842076</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>579.3725848165558</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>20103.2095380974</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>705.7474057633924</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$530,A15,'Species'!$U$2:$U$530))</x:f>
-        <x:v>14187787.979030125</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.7629579410842076</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>579.3725848165558</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>11647248.473196328</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2540539.505833797</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2181235775711585</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.21812357757115855</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>39093.4816637818</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.4545345116131156</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>284.7964107286477</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>39093.4816637818</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>360.22194048328157</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$530,A16,'Species'!$U$2:$U$530))</x:f>
-        <x:v>14082329.825175067</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.4545345116131156</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>284.7964107286477</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>11133683.26073126</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2948646.564443808</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2648401697256602</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.26484016972566016</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>47660.05075680129</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1282709390553856</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>134.3602920152884</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>47660.05075680129</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>382.40510827438203</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$530,A17,'Species'!$U$2:$U$530))</x:f>
-        <x:v>18225446.87001714</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1282709390553856</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>134.3602920152884</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>6403618.337147288</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>11821828.532869853</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.846116978004703</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.846116978004703</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>14379.273094728402</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.563782837430848</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>366.25438873081254</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>14379.273094728402</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>982.8884289131859</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$530,A18,'Species'!$U$2:$U$530))</x:f>
-        <x:v>14133221.140991243</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.563782837430848</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>366.25438873081254</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>5266471.87770317</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>8866749.263288073</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>2.683622255883965</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>1.683622255883965</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>6505.5091501904</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.0228820638952754</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>10.54100608155994</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>6505.5091501904</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>11.13631772733072</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$530,A19,'Species'!$U$2:$U$530))</x:f>
-        <x:v>72447.41687457755</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.0228820638952754</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>10.54100608155994</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>68574.61151580085</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>3872.8053587767063</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0564757899923989</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.05647578999239888</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>15581.143048052601</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1165297802685252</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>130.77652114017636</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>15581.143048052601</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>185.839071859603</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$530,A20,'Species'!$U$2:$U$530))</x:f>
-        <x:v>2895585.1625618013</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1165297802685252</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>130.77652114017636</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>2037647.683211763</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>857937.4793500383</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.4210430912167051</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.4210430912167052</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>436.5280404373</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.254749439693205</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>179.78333802943985</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>436.5280404373</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>180.45965868979087</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$530,A21,'Species'!$U$2:$U$530))</x:f>
-        <x:v>78775.70118583838</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.254749439693205</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>179.78333802943985</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>78480.46825326809</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>295.23293257028854</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0037618650747282</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0037618650747282515</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>1445.0597983049004</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.5851845014473867</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>384.75520299134956</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>1445.0597983049004</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>387.40342416512016</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$530,A22,'Species'!$U$2:$U$530))</x:f>
-        <x:v>559821.1139866763</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.5851845014473867</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>384.75520299134956</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>555994.2760314406</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>3826.8379552357364</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0068828729363022</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.006882872936302198</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1751.2008374189</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.0151744135927077</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>103.55579654744751</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1751.2008374189</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>330.3848911760022</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$530,A23,'Species'!$U$2:$U$530))</x:f>
-        <x:v>578570.2980979672</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.0151744135927077</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>103.55579654744751</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>181346.9976334713</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>397223.3004644959</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>3.190404614623629</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>2.1904046146236293</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>725.4803693483999</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.379850560893435</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>239.80076315831843</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>725.4803693483999</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>251.03778071903292</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$530,A24,'Species'!$U$2:$U$530))</x:f>
-        <x:v>182122.98187644663</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.379850560893435</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>239.80076315831843</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>173970.74622612502</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>8152.235650321614</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.046859807336375</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.04685980733637504</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>194.4130665186</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.7065692163964754</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>508.8259081476797</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>194.4130665186</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>547.5518392733687</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$530,A25,'Species'!$U$2:$U$530))</x:f>
-        <x:v>106451.2321510352</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.7065692163964754</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>508.8259081476797</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>98922.40512710191</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>7528.827023933292</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0761084105694738</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.0761084105694738</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>286.9279815809</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.5880761066873768</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>387.32551472043315</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>286.9279815809</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>396.57163083088125</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$530,A26,'Species'!$U$2:$U$530))</x:f>
-        <x:v>113787.49758655057</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.5880761066873768</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>387.32551472043315</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>111134.52815351705</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>2652.9694330335187</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0238716938570955</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.02387169385709549</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>4.4412573628</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>4.314992910993796</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>2065.346442802762</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>4.4412573628</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>2112.3348388079226</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$530,A27,'Species'!$U$2:$U$530))</x:f>
-        <x:v>9381.422655554637</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>4.314992910993796</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>2065.346442802762</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>9172.735095830556</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>208.68755972408144</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.022750854302872</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.022750854302871982</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5af5ebe669a146c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b34370c889543cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38490,7 +37041,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -38589,7 +37140,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>159135782.88848546</x:v>
+        <x:v>107374397.92635019</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -38603,7 +37154,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>159135782.88848546</x:v>
+        <x:v>113696362.2670475</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -38617,7 +37168,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-51761384.96213524</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -38631,7 +37182,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-45439420.62143794</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -38642,9 +37193,9 @@
         <x:v>EEZ_036</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -38656,47 +37207,19 @@
         <x:v>EEZ_036</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_036</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_036</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7dc73a62c894489"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29c2a1b4ca3b4c8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38743,7 +37266,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
